--- a/Horarios/HorarioWAN_Ago2026.xlsx
+++ b/Horarios/HorarioWAN_Ago2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{B7FF1D9A-58DB-4543-A46C-6218F66CDCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{728A661B-9903-4E99-9FDD-8E5F76ADB46E}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{B7FF1D9A-58DB-4543-A46C-6218F66CDCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00EE86D-66A4-4C0D-8574-8755C669C7BB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -405,16 +405,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -424,39 +457,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -813,13 +813,13 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -827,21 +827,21 @@
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="22" t="s">
         <v>5</v>
       </c>
     </row>
@@ -849,9 +849,9 @@
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -871,13 +871,13 @@
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="C9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>3</v>
       </c>
     </row>
@@ -885,21 +885,21 @@
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="12"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="22" t="s">
         <v>5</v>
       </c>
     </row>
@@ -907,9 +907,9 @@
       <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
@@ -926,13 +926,13 @@
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="C15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -940,21 +940,21 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="22" t="s">
         <v>5</v>
       </c>
     </row>
@@ -962,9 +962,9 @@
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
@@ -981,13 +981,13 @@
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="C21" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="21" t="s">
         <v>3</v>
       </c>
     </row>
@@ -995,18 +995,16 @@
       <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="12"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="23"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="11" t="s">
+      <c r="C23" s="27"/>
+      <c r="D23" s="22" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="19" t="s">
@@ -1017,8 +1015,8 @@
       <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="20"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1033,13 +1031,13 @@
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="23" t="s">
+      <c r="C27" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1047,27 +1045,29 @@
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="24"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="21" t="s">
+      <c r="C29" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="24"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="25"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -1087,13 +1087,13 @@
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="23" t="s">
+      <c r="C33" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1101,29 +1101,29 @@
       <c r="B34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="24"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="24"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="25"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="13"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
@@ -1143,13 +1143,13 @@
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="13" t="s">
+      <c r="C39" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1157,21 +1157,21 @@
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="E41" s="14" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1179,9 +1179,9 @@
       <c r="B42" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -1201,13 +1201,13 @@
       <c r="B45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="13" t="s">
+      <c r="D45" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1215,16 +1215,16 @@
       <c r="B46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="28"/>
-      <c r="D47" s="21" t="s">
+      <c r="C47" s="16"/>
+      <c r="D47" s="14" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="19" t="s">
@@ -1235,8 +1235,8 @@
       <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="22"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="15"/>
       <c r="E48" s="20"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
@@ -1257,13 +1257,13 @@
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="18" t="s">
+      <c r="D51" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="21" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1271,19 +1271,19 @@
       <c r="B52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="18"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="21" t="s">
+      <c r="C53" s="16"/>
+      <c r="D53" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E53" s="14" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1291,9 +1291,9 @@
       <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="25"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -1313,13 +1313,13 @@
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1327,25 +1327,25 @@
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="5"/>
@@ -1355,6 +1355,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
     <mergeCell ref="C41:C42"/>
@@ -1371,42 +1407,6 @@
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_Ago2026.xlsx
+++ b/Horarios/HorarioWAN_Ago2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{B7FF1D9A-58DB-4543-A46C-6218F66CDCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00EE86D-66A4-4C0D-8574-8755C669C7BB}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{B7FF1D9A-58DB-4543-A46C-6218F66CDCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94A0E7F5-F7DE-48F3-99EF-013930928F09}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="27">
   <si>
     <t>MARTES</t>
   </si>
@@ -89,9 +89,6 @@
   <si>
     <t>EXAMEN INTEGRADOR 
 (EVIDENCIA 1)</t>
-  </si>
-  <si>
-    <t>EVALUACIÓN DE ACTIVIDADES</t>
   </si>
   <si>
     <r>
@@ -405,24 +402,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -433,9 +433,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -791,7 +788,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -813,13 +810,13 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -828,8 +825,8 @@
         <v>14</v>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
@@ -861,7 +858,7 @@
     </row>
     <row r="8" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -871,13 +868,13 @@
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="C9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -885,8 +882,8 @@
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
@@ -916,7 +913,7 @@
     </row>
     <row r="14" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -926,23 +923,23 @@
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>6</v>
+      <c r="C15" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
@@ -971,7 +968,7 @@
     </row>
     <row r="20" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -984,11 +981,11 @@
       <c r="C21" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>3</v>
+      <c r="D21" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
@@ -996,8 +993,8 @@
         <v>14</v>
       </c>
       <c r="C22" s="27"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="23"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
@@ -1007,7 +1004,7 @@
       <c r="D23" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="20" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1017,11 +1014,11 @@
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1031,13 +1028,13 @@
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1045,9 +1042,9 @@
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="18"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
@@ -1056,18 +1053,18 @@
       <c r="C29" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="12"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="23"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -1077,7 +1074,7 @@
     </row>
     <row r="32" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -1087,13 +1084,13 @@
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="11" t="s">
+      <c r="C33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="14" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1101,29 +1098,29 @@
       <c r="B34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="12"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="17"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="17"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
@@ -1133,7 +1130,7 @@
     </row>
     <row r="38" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -1143,13 +1140,13 @@
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="C39" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1157,31 +1154,31 @@
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="14" t="s">
-        <v>7</v>
+      <c r="E41" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -1191,7 +1188,7 @@
     </row>
     <row r="44" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -1204,10 +1201,10 @@
       <c r="C45" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="17" t="s">
+      <c r="D45" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1215,19 +1212,21 @@
       <c r="B46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="14" t="s">
+      <c r="C47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="D47" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="20" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1236,8 +1235,8 @@
         <v>13</v>
       </c>
       <c r="C48" s="13"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="20"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
@@ -1247,7 +1246,7 @@
     </row>
     <row r="50" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -1257,13 +1256,13 @@
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="21" t="s">
+      <c r="D51" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1271,19 +1270,19 @@
       <c r="B52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="21"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="11"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="14" t="s">
+      <c r="C53" s="15"/>
+      <c r="D53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1291,9 +1290,9 @@
       <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -1303,7 +1302,7 @@
     </row>
     <row r="56" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
@@ -1313,39 +1312,39 @@
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="14" t="s">
         <v>15</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="17"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="17"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="5"/>
@@ -1354,13 +1353,12 @@
       <c r="E61" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="C15:C16"/>
+  <mergeCells count="53">
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C5:C6"/>
@@ -1376,7 +1374,8 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E53:E54"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="D39:D40"/>
@@ -1391,12 +1390,14 @@
     <mergeCell ref="E33:E36"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="D35:D36"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C47:C48"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="D41:D42"/>
     <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C45:C48"/>
     <mergeCell ref="D45:D46"/>
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="D47:D48"/>
@@ -1406,7 +1407,6 @@
     <mergeCell ref="D51:D52"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
